--- a/0000_InglesConIA/verbos.xlsx
+++ b/0000_InglesConIA/verbos.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\0000_InglesConIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF3870B-5843-4F8D-8714-EE764C81B529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356B1A38-4124-4C97-BF5E-2CE3EE4A5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ToBe" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="181">
   <si>
     <t>I</t>
   </si>
@@ -376,6 +377,198 @@
   </si>
   <si>
     <t>El Present Continuous describe un comportamiento temporal — cómo se está comportando alguien en este momento, sin que sea su forma habitual de ser</t>
+  </si>
+  <si>
+    <t>I have been</t>
+  </si>
+  <si>
+    <t>you have been</t>
+  </si>
+  <si>
+    <t>we have been</t>
+  </si>
+  <si>
+    <t>they have been</t>
+  </si>
+  <si>
+    <t>he has been</t>
+  </si>
+  <si>
+    <t>she has been</t>
+  </si>
+  <si>
+    <t>it has been</t>
+  </si>
+  <si>
+    <t>I´ve been</t>
+  </si>
+  <si>
+    <t>you've been</t>
+  </si>
+  <si>
+    <t>we've been</t>
+  </si>
+  <si>
+    <t>they've been</t>
+  </si>
+  <si>
+    <t>he's been</t>
+  </si>
+  <si>
+    <t>she's been</t>
+  </si>
+  <si>
+    <t>it´s been</t>
+  </si>
+  <si>
+    <t>yo he sido / yo he estado</t>
+  </si>
+  <si>
+    <t>tu has sido/ tu has estado</t>
+  </si>
+  <si>
+    <t>el ha sido/ el ha estado</t>
+  </si>
+  <si>
+    <t>ella ha sido/ ella ha estado</t>
+  </si>
+  <si>
+    <t>nosotros hemos sido / nosotros hemos estado</t>
+  </si>
+  <si>
+    <t>eso ha sido/eso ha estado</t>
+  </si>
+  <si>
+    <t>ellos han sido / ellos han estado</t>
+  </si>
+  <si>
+    <t>I have not been</t>
+  </si>
+  <si>
+    <t>you have not been</t>
+  </si>
+  <si>
+    <t>he has not been</t>
+  </si>
+  <si>
+    <t>she has not been</t>
+  </si>
+  <si>
+    <t>it has not been</t>
+  </si>
+  <si>
+    <t>we have not been</t>
+  </si>
+  <si>
+    <t>they have not been</t>
+  </si>
+  <si>
+    <t>yo no he sido / yo no he estado</t>
+  </si>
+  <si>
+    <t>tu no has sido / tu no has estado</t>
+  </si>
+  <si>
+    <t>el no ha sido / el no ha estado</t>
+  </si>
+  <si>
+    <t>ella no ha sido / ella no ha estado</t>
+  </si>
+  <si>
+    <t>eso no ha sido / eso no ha estado</t>
+  </si>
+  <si>
+    <t>nosotros no hemos sido / nosotros no hemos estado</t>
+  </si>
+  <si>
+    <t>ellos no han sido / ellos no han estado</t>
+  </si>
+  <si>
+    <t>have I been ?</t>
+  </si>
+  <si>
+    <t>have you been ?.</t>
+  </si>
+  <si>
+    <t>has he been ?</t>
+  </si>
+  <si>
+    <t>has she been ?.</t>
+  </si>
+  <si>
+    <t>has it being ?.</t>
+  </si>
+  <si>
+    <t>have we been ?.</t>
+  </si>
+  <si>
+    <t>have they been ?.</t>
+  </si>
+  <si>
+    <t>ellos han sido ?. Ellos han estado ?.</t>
+  </si>
+  <si>
+    <t>yo he sido ? / yo he estado ?.</t>
+  </si>
+  <si>
+    <t>tu has sido ? / tu has estado ?.</t>
+  </si>
+  <si>
+    <t>el ha sido ? / el ha estado ?.</t>
+  </si>
+  <si>
+    <t>ella ha sido ? / ella ha estado ?.</t>
+  </si>
+  <si>
+    <t>eso ha sido ? / eso ha estado ?.</t>
+  </si>
+  <si>
+    <t>nosotros hemos sido ? / nosotros hemos estado ?.</t>
+  </si>
+  <si>
+    <t>yo</t>
+  </si>
+  <si>
+    <t>tu</t>
+  </si>
+  <si>
+    <t>el</t>
+  </si>
+  <si>
+    <t>ella</t>
+  </si>
+  <si>
+    <t>eso</t>
+  </si>
+  <si>
+    <t>nosotros</t>
+  </si>
+  <si>
+    <t>ellos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am </t>
+  </si>
+  <si>
+    <t>Afirmativa</t>
+  </si>
+  <si>
+    <t>Interrogativa</t>
+  </si>
+  <si>
+    <t>Negativa</t>
+  </si>
+  <si>
+    <t>yo are being</t>
+  </si>
+  <si>
+    <t>are you being ?.</t>
+  </si>
+  <si>
+    <t>are we being ?.</t>
+  </si>
+  <si>
+    <t>are they being ?.</t>
   </si>
 </sst>
 </file>
@@ -451,9 +644,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -466,16 +665,15 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,74 +954,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K34"/>
+  <dimension ref="B2:K41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="66.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="G5" s="3" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="J5" s="4" t="s">
+      <c r="H5" s="5"/>
+      <c r="J5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
@@ -1034,60 +1232,60 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="G19" s="3" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="G19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="J19" s="4" t="s">
+      <c r="H19" s="5"/>
+      <c r="J19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="4"/>
+      <c r="K19" s="6"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
@@ -1298,58 +1496,58 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-    </row>
-    <row r="32" spans="2:11" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="G33" s="3" t="s">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="G33" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H33" s="3"/>
-      <c r="J33" s="4" t="s">
+      <c r="H33" s="5"/>
+      <c r="J33" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K33" s="4"/>
+      <c r="K33" s="6"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
@@ -1377,8 +1575,197 @@
         <v>23</v>
       </c>
     </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" t="s">
+        <v>160</v>
+      </c>
+      <c r="J35" t="s">
+        <v>138</v>
+      </c>
+      <c r="K35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" t="s">
+        <v>161</v>
+      </c>
+      <c r="J36" t="s">
+        <v>139</v>
+      </c>
+      <c r="K36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" t="s">
+        <v>154</v>
+      </c>
+      <c r="H37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J37" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D38" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" t="s">
+        <v>163</v>
+      </c>
+      <c r="J38" t="s">
+        <v>141</v>
+      </c>
+      <c r="K38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" t="s">
+        <v>164</v>
+      </c>
+      <c r="J39" t="s">
+        <v>142</v>
+      </c>
+      <c r="K39" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" t="s">
+        <v>165</v>
+      </c>
+      <c r="J40" t="s">
+        <v>143</v>
+      </c>
+      <c r="K40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41" t="s">
+        <v>158</v>
+      </c>
+      <c r="H41" t="s">
+        <v>159</v>
+      </c>
+      <c r="J41" t="s">
+        <v>144</v>
+      </c>
+      <c r="K41" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B30:K31"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="G5:H5"/>
@@ -1386,13 +1773,248 @@
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B16:K17"/>
     <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B30:K31"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE73917-CD0D-4C39-B239-E8043EB5BB19}">
+  <dimension ref="C1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/0000_InglesConIA/verbos.xlsx
+++ b/0000_InglesConIA/verbos.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\0000_InglesConIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356B1A38-4124-4C97-BF5E-2CE3EE4A5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C7E09-13B0-4463-8CF3-01C980F28FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ToBe" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="166">
   <si>
     <t>I</t>
   </si>
@@ -524,51 +523,6 @@
   </si>
   <si>
     <t>nosotros hemos sido ? / nosotros hemos estado ?.</t>
-  </si>
-  <si>
-    <t>yo</t>
-  </si>
-  <si>
-    <t>tu</t>
-  </si>
-  <si>
-    <t>el</t>
-  </si>
-  <si>
-    <t>ella</t>
-  </si>
-  <si>
-    <t>eso</t>
-  </si>
-  <si>
-    <t>nosotros</t>
-  </si>
-  <si>
-    <t>ellos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I am </t>
-  </si>
-  <si>
-    <t>Afirmativa</t>
-  </si>
-  <si>
-    <t>Interrogativa</t>
-  </si>
-  <si>
-    <t>Negativa</t>
-  </si>
-  <si>
-    <t>yo are being</t>
-  </si>
-  <si>
-    <t>are you being ?.</t>
-  </si>
-  <si>
-    <t>are we being ?.</t>
-  </si>
-  <si>
-    <t>are they being ?.</t>
   </si>
 </sst>
 </file>
@@ -644,14 +598,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -665,14 +616,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,34 +912,34 @@
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="66.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1008,20 +956,20 @@
       <c r="K4" s="8"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="G5" s="5" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="J5" s="6" t="s">
+      <c r="H5" s="4"/>
+      <c r="J5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K5" s="6"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
@@ -1232,60 +1180,60 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="G19" s="5" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="G19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="J19" s="6" t="s">
+      <c r="H19" s="4"/>
+      <c r="J19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="6"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
@@ -1496,30 +1444,30 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
     </row>
     <row r="32" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
@@ -1534,20 +1482,20 @@
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="G33" s="5" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="G33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="J33" s="6" t="s">
+      <c r="H33" s="4"/>
+      <c r="J33" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K33" s="6"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
@@ -1759,6 +1707,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="B16:K17"/>
+    <mergeCell ref="B4:K4"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="J19:K19"/>
@@ -1766,255 +1721,6 @@
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B2:K3"/>
-    <mergeCell ref="B16:K17"/>
-    <mergeCell ref="B4:K4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE73917-CD0D-4C39-B239-E8043EB5BB19}">
-  <dimension ref="C1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="E1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-    </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>177</v>
-      </c>
-      <c r="I4" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" t="s">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
